--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5478-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5478-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2373AC05-AD09-48CB-AC05-9BDC6D1CC11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{078BD5E6-CB6F-4FE9-A47A-12EEC24D8958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{83C5DC22-672F-491A-AE69-0FBF170FB9AB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{481435FA-D13D-486D-99CB-95F18642B721}"/>
   </bookViews>
   <sheets>
     <sheet name="5478-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1574,30 +1574,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CCBE8B-E7E8-42D8-A7A5-382922B181BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{169F2833-354B-4882-AB3C-CD11E337D6D8}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1787,7 +1787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>2024</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>8.3800000000000008</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2023</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2022</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2021</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>2020</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2019</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>2018</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2017</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>2016</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2015</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>2014</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2013</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>2012</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2011</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>2010</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2009</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>2008</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>2007</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <v>2006</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>2005</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>2004</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>2003</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>2002</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>2001</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>2000</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="42">
         <v>1999</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="44"/>
       <c r="B52" s="45"/>
       <c r="C52" s="21" t="s">
@@ -5239,7 +5239,7 @@
       <c r="W52" s="51"/>
       <c r="X52" s="47"/>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>1998</v>
       </c>
@@ -5311,7 +5311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="38">
         <v>1997</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="40" t="s">
         <v>66</v>
       </c>
